--- a/import-files/App Upper Rankings.xlsx
+++ b/import-files/App Upper Rankings.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\New folder (2)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871F19CA-A704-4828-B63C-08D2CC9AA0A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14F30D4-E1FB-43EA-8F0D-2A7DC724FDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25974" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -492,47 +492,7 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{D9E2E6CB-7849-4D55-977E-8284C9300F64}"/>
     <cellStyle name="Percent 2" xfId="3" xr:uid="{7C6C4FDE-AD67-44C6-9117-09EAF289A91F}"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -849,7 +809,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.875" bestFit="1" customWidth="1"/>
@@ -937,41 +897,41 @@
         <v>20</v>
       </c>
       <c r="E2" s="10">
-        <v>30799</v>
+        <v>36763</v>
       </c>
       <c r="F2" s="10">
-        <v>1204</v>
+        <v>1441</v>
       </c>
       <c r="G2" s="11">
-        <v>76.74169435215947</v>
+        <v>76.536433032616245</v>
       </c>
       <c r="H2" s="12">
-        <v>1.765625</v>
+        <v>1.736842105263158</v>
       </c>
       <c r="I2" s="10">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="J2" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K2" s="10"/>
       <c r="L2" s="10">
         <v>161</v>
       </c>
       <c r="M2" s="10">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="N2" s="10">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="O2" s="13">
-        <v>0.78125</v>
+        <v>0.77631578947368418</v>
       </c>
       <c r="P2" s="12">
-        <v>77.156686046511624</v>
+        <v>76.864976807041899</v>
       </c>
       <c r="Q2" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -988,245 +948,245 @@
         <v>24</v>
       </c>
       <c r="E3" s="10">
-        <v>36789</v>
+        <v>42714</v>
       </c>
       <c r="F3" s="10">
-        <v>1485</v>
+        <v>1712</v>
       </c>
       <c r="G3" s="11">
-        <v>74.321212121212113</v>
+        <v>74.849299065420567</v>
       </c>
       <c r="H3" s="12">
-        <v>1.736842105263158</v>
+        <v>1.7954545454545454</v>
       </c>
       <c r="I3" s="10">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="J3" s="10">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K3" s="10"/>
       <c r="L3" s="10">
         <v>147</v>
       </c>
       <c r="M3" s="10">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="N3" s="10">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="O3" s="13">
-        <v>0.68421052631578949</v>
+        <v>0.68181818181818177</v>
       </c>
       <c r="P3" s="12">
-        <v>72.551164274322161</v>
+        <v>72.849054800339843</v>
       </c>
       <c r="Q3" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E4" s="10">
-        <v>36328</v>
+        <v>42738</v>
       </c>
       <c r="F4" s="10">
-        <v>1514</v>
+        <v>1730</v>
       </c>
       <c r="G4" s="11">
-        <v>71.984147952443863</v>
+        <v>74.1121387283237</v>
       </c>
       <c r="H4" s="12">
-        <v>1.4736842105263157</v>
+        <v>1.4204545454545454</v>
       </c>
       <c r="I4" s="10">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="J4" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K4" s="10"/>
       <c r="L4" s="10">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="M4" s="10">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="N4" s="10">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="O4" s="13">
-        <v>0.73684210526315785</v>
+        <v>0.69318181818181823</v>
       </c>
       <c r="P4" s="12">
-        <v>72.494166724605435</v>
+        <v>72.673951655281144</v>
       </c>
       <c r="Q4" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E5" s="10">
-        <v>36761</v>
+        <v>41904</v>
       </c>
       <c r="F5" s="10">
-        <v>1520</v>
+        <v>1749</v>
       </c>
       <c r="G5" s="11">
-        <v>72.554605263157896</v>
+        <v>71.876500857632934</v>
       </c>
       <c r="H5" s="12">
-        <v>1.3552631578947369</v>
+        <v>1.4545454545454546</v>
       </c>
       <c r="I5" s="10">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="J5" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K5" s="10"/>
       <c r="L5" s="10">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="M5" s="10">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="N5" s="10">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="O5" s="13">
-        <v>0.68421052631578949</v>
+        <v>0.68181818181818177</v>
       </c>
       <c r="P5" s="12">
-        <v>71.314539473684206</v>
+        <v>70.768096054888503</v>
       </c>
       <c r="Q5" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="E6" s="10">
-        <v>36440</v>
+        <v>36195</v>
       </c>
       <c r="F6" s="10">
-        <v>1520</v>
+        <v>1495</v>
       </c>
       <c r="G6" s="11">
-        <v>71.921052631578945</v>
+        <v>72.632107023411379</v>
       </c>
       <c r="H6" s="12">
-        <v>1.3289473684210527</v>
+        <v>1.5657894736842106</v>
       </c>
       <c r="I6" s="10">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="J6" s="10">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K6" s="10"/>
       <c r="L6" s="10">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="M6" s="10">
         <v>76</v>
       </c>
       <c r="N6" s="10">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="O6" s="13">
-        <v>0.67105263157894735</v>
+        <v>0.61842105263157898</v>
       </c>
       <c r="P6" s="12">
-        <v>70.476315789473674</v>
+        <v>69.395106495335341</v>
       </c>
       <c r="Q6" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E7" s="10">
-        <v>30507</v>
+        <v>41949</v>
       </c>
       <c r="F7" s="10">
-        <v>1250</v>
+        <v>1777</v>
       </c>
       <c r="G7" s="11">
-        <v>73.216800000000006</v>
+        <v>70.819921215531792</v>
       </c>
       <c r="H7" s="12">
-        <v>1.59375</v>
+        <v>1.2840909090909092</v>
       </c>
       <c r="I7" s="10">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="J7" s="10">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K7" s="10"/>
       <c r="L7" s="10">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="M7" s="10">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="N7" s="10">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="O7" s="13">
-        <v>0.609375</v>
+        <v>0.64772727272727271</v>
       </c>
       <c r="P7" s="12">
-        <v>69.533010000000004</v>
+        <v>69.005763032690425</v>
       </c>
       <c r="Q7" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -1243,41 +1203,41 @@
         <v>41</v>
       </c>
       <c r="E8" s="10">
-        <v>34727</v>
+        <v>40241</v>
       </c>
       <c r="F8" s="10">
-        <v>1475</v>
+        <v>1713</v>
       </c>
       <c r="G8" s="11">
-        <v>70.631186440677965</v>
+        <v>70.474605954465844</v>
       </c>
       <c r="H8" s="12">
-        <v>1.5694444444444444</v>
+        <v>1.4761904761904763</v>
       </c>
       <c r="I8" s="10">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="J8" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K8" s="10"/>
       <c r="L8" s="10">
         <v>83</v>
       </c>
       <c r="M8" s="10">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="N8" s="10">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="O8" s="13">
-        <v>0.63888888888888884</v>
+        <v>0.63095238095238093</v>
       </c>
       <c r="P8" s="12">
-        <v>68.608497175141238</v>
+        <v>68.26079559669752</v>
       </c>
       <c r="Q8" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -1294,19 +1254,19 @@
         <v>20</v>
       </c>
       <c r="E9" s="10">
-        <v>36957</v>
+        <v>42744</v>
       </c>
       <c r="F9" s="10">
-        <v>1586</v>
+        <v>1846</v>
       </c>
       <c r="G9" s="11">
-        <v>69.906052963430014</v>
+        <v>69.464788732394368</v>
       </c>
       <c r="H9" s="12">
-        <v>1.5263157894736843</v>
+        <v>1.4772727272727273</v>
       </c>
       <c r="I9" s="10">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="J9" s="10">
         <v>3</v>
@@ -1316,69 +1276,67 @@
         <v>143</v>
       </c>
       <c r="M9" s="10">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="N9" s="10">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="O9" s="13">
-        <v>0.64473684210526316</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="P9" s="12">
-        <v>68.276342337558901</v>
+        <v>67.716261203585148</v>
       </c>
       <c r="Q9" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E10" s="10">
-        <v>36595</v>
+        <v>41975</v>
       </c>
       <c r="F10" s="10">
-        <v>1551</v>
+        <v>1805</v>
       </c>
       <c r="G10" s="11">
-        <v>70.783365570599614</v>
+        <v>69.76454293628808</v>
       </c>
       <c r="H10" s="12">
-        <v>1.5394736842105263</v>
+        <v>1.6590909090909092</v>
       </c>
       <c r="I10" s="10">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="J10" s="10">
-        <v>4</v>
-      </c>
-      <c r="K10" s="10">
-        <v>1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="K10" s="10"/>
       <c r="L10" s="10">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="M10" s="10">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="N10" s="10">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="O10" s="13">
-        <v>0.61842105263157898</v>
+        <v>0.625</v>
       </c>
       <c r="P10" s="12">
-        <v>68.100987478367102</v>
+        <v>67.585180055401651</v>
       </c>
       <c r="Q10" s="1">
         <v>3</v>
@@ -1398,92 +1356,94 @@
         <v>20</v>
       </c>
       <c r="E11" s="10">
-        <v>36286</v>
+        <v>41994</v>
       </c>
       <c r="F11" s="10">
-        <v>1575</v>
+        <v>1834</v>
       </c>
       <c r="G11" s="11">
-        <v>69.116190476190468</v>
+        <v>68.692475463467829</v>
       </c>
       <c r="H11" s="12">
-        <v>1.6842105263157894</v>
+        <v>1.6704545454545454</v>
       </c>
       <c r="I11" s="10">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="J11" s="10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K11" s="10"/>
       <c r="L11" s="10">
         <v>104</v>
       </c>
       <c r="M11" s="10">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="N11" s="10">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="O11" s="13">
-        <v>0.63157894736842102</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="P11" s="12">
-        <v>67.328701754385946</v>
+        <v>67.17564191533657</v>
       </c>
       <c r="Q11" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="E12" s="10">
-        <v>36414</v>
+        <v>42059</v>
       </c>
       <c r="F12" s="10">
-        <v>1581</v>
+        <v>1813</v>
       </c>
       <c r="G12" s="11">
-        <v>69.096774193548384</v>
+        <v>69.59569773855489</v>
       </c>
       <c r="H12" s="12">
-        <v>1.631578947368421</v>
+        <v>1.4318181818181819</v>
       </c>
       <c r="I12" s="10">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J12" s="10">
-        <v>7</v>
-      </c>
-      <c r="K12" s="10"/>
+        <v>4</v>
+      </c>
+      <c r="K12" s="10">
+        <v>1</v>
+      </c>
       <c r="L12" s="10">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="M12" s="10">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="N12" s="10">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="O12" s="13">
-        <v>0.63157894736842102</v>
+        <v>0.60227272727272729</v>
       </c>
       <c r="P12" s="12">
-        <v>67.315110356536493</v>
+        <v>66.785170235170241</v>
       </c>
       <c r="Q12" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -1500,41 +1460,41 @@
         <v>24</v>
       </c>
       <c r="E13" s="10">
-        <v>36093</v>
+        <v>41526</v>
       </c>
       <c r="F13" s="10">
-        <v>1594</v>
+        <v>1857</v>
       </c>
       <c r="G13" s="11">
-        <v>67.929109159347561</v>
+        <v>67.08562197092084</v>
       </c>
       <c r="H13" s="12">
-        <v>1.3157894736842106</v>
+        <v>1.3522727272727273</v>
       </c>
       <c r="I13" s="10">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="J13" s="10">
         <v>5</v>
       </c>
       <c r="K13" s="10"/>
       <c r="L13" s="10">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="M13" s="10">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="N13" s="10">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="O13" s="13">
-        <v>0.57894736842105265</v>
+        <v>0.57954545454545459</v>
       </c>
       <c r="P13" s="12">
-        <v>64.918797464174872</v>
+        <v>64.346299016008217</v>
       </c>
       <c r="Q13" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -1551,38 +1511,38 @@
         <v>20</v>
       </c>
       <c r="E14" s="10">
-        <v>36268</v>
+        <v>41974</v>
       </c>
       <c r="F14" s="10">
-        <v>1643</v>
+        <v>1876</v>
       </c>
       <c r="G14" s="11">
-        <v>66.222763237979308</v>
+        <v>67.122601279317692</v>
       </c>
       <c r="H14" s="12">
-        <v>1.486842105263158</v>
+        <v>1.5113636363636365</v>
       </c>
       <c r="I14" s="10">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="J14" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K14" s="10"/>
       <c r="L14" s="10">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="M14" s="10">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="N14" s="10">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O14" s="13">
-        <v>0.59210526315789469</v>
+        <v>0.56818181818181823</v>
       </c>
       <c r="P14" s="12">
-        <v>64.119092161322357</v>
+        <v>64.031275440976927</v>
       </c>
       <c r="Q14" s="1">
         <v>2</v>
@@ -1602,19 +1562,19 @@
         <v>41</v>
       </c>
       <c r="E15" s="10">
-        <v>35401</v>
+        <v>40828</v>
       </c>
       <c r="F15" s="10">
-        <v>1602</v>
+        <v>1829</v>
       </c>
       <c r="G15" s="11">
-        <v>66.294007490636702</v>
+        <v>66.967741935483872</v>
       </c>
       <c r="H15" s="12">
-        <v>1.4473684210526316</v>
+        <v>1.4772727272727273</v>
       </c>
       <c r="I15" s="10">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="J15" s="10">
         <v>4</v>
@@ -1626,19 +1586,19 @@
         <v>150</v>
       </c>
       <c r="M15" s="10">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="N15" s="10">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="O15" s="13">
-        <v>0.53947368421052633</v>
+        <v>0.53409090909090906</v>
       </c>
       <c r="P15" s="12">
-        <v>62.590015769761479</v>
+        <v>62.900146627565974</v>
       </c>
       <c r="Q15" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -1655,19 +1615,19 @@
         <v>20</v>
       </c>
       <c r="E16" s="10">
-        <v>35999</v>
+        <v>42059</v>
       </c>
       <c r="F16" s="10">
-        <v>1653</v>
+        <v>1909</v>
       </c>
       <c r="G16" s="11">
-        <v>65.333938294010892</v>
+        <v>66.095861707700365</v>
       </c>
       <c r="H16" s="12">
-        <v>1.2105263157894737</v>
+        <v>1.2840909090909092</v>
       </c>
       <c r="I16" s="10">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="J16" s="10">
         <v>9</v>
@@ -1677,16 +1637,16 @@
         <v>160</v>
       </c>
       <c r="M16" s="10">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="N16" s="10">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O16" s="13">
-        <v>0.55263157894736847</v>
+        <v>0.53409090909090906</v>
       </c>
       <c r="P16" s="12">
-        <v>62.312704174228678</v>
+        <v>62.289830468117529</v>
       </c>
       <c r="Q16" s="1">
         <v>1</v>
@@ -1694,403 +1654,407 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E17" s="10">
-        <v>30339</v>
+        <v>41113</v>
       </c>
       <c r="F17" s="10">
-        <v>1463</v>
+        <v>1896</v>
       </c>
       <c r="G17" s="11">
-        <v>62.212576896787425</v>
+        <v>65.052215189873422</v>
       </c>
       <c r="H17" s="12">
-        <v>1.3125</v>
+        <v>1.4431818181818181</v>
       </c>
       <c r="I17" s="10">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="J17" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K17" s="10"/>
       <c r="L17" s="10">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="M17" s="10">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="N17" s="10">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="O17" s="13">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="P17" s="12">
-        <v>62.298803827751193</v>
-      </c>
-      <c r="Q17" s="1"/>
+        <v>60.536550632911393</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>5</v>
+      </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>41</v>
       </c>
       <c r="E18" s="10">
-        <v>29641</v>
+        <v>35610</v>
       </c>
       <c r="F18" s="10">
-        <v>1361</v>
+        <v>1726</v>
       </c>
       <c r="G18" s="11">
-        <v>65.336517266715646</v>
+        <v>61.894553881807653</v>
       </c>
       <c r="H18" s="12">
-        <v>1.703125</v>
+        <v>1.236842105263158</v>
       </c>
       <c r="I18" s="10">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="J18" s="10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K18" s="10"/>
       <c r="L18" s="10">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="M18" s="10">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="N18" s="10">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="O18" s="13">
-        <v>0.53125</v>
+        <v>0.56578947368421051</v>
       </c>
       <c r="P18" s="12">
-        <v>61.673062086700952</v>
-      </c>
-      <c r="Q18" s="1"/>
+        <v>60.299871927791671</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>41</v>
       </c>
       <c r="E19" s="10">
-        <v>24560</v>
+        <v>35082</v>
       </c>
       <c r="F19" s="10">
-        <v>1164</v>
+        <v>1628</v>
       </c>
       <c r="G19" s="11">
-        <v>63.298969072164951</v>
+        <v>64.647420147420149</v>
       </c>
       <c r="H19" s="12">
-        <v>1.1153846153846154</v>
+        <v>1.6842105263157894</v>
       </c>
       <c r="I19" s="10">
-        <v>58</v>
+        <v>128</v>
       </c>
       <c r="J19" s="10">
-        <v>4</v>
-      </c>
-      <c r="K19" s="10">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K19" s="10"/>
       <c r="L19" s="10">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M19" s="10">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="N19" s="10">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="O19" s="13">
-        <v>0.53846153846153844</v>
+        <v>0.5</v>
       </c>
       <c r="P19" s="12">
-        <v>60.463124504361616</v>
+        <v>60.253194103194105</v>
       </c>
       <c r="Q19" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E20" s="10">
-        <v>35057</v>
+        <v>22475</v>
       </c>
       <c r="F20" s="10">
-        <v>1654</v>
+        <v>1059</v>
       </c>
       <c r="G20" s="11">
-        <v>63.585852478839179</v>
+        <v>63.668555240793197</v>
       </c>
       <c r="H20" s="12">
-        <v>1.2894736842105263</v>
+        <v>1.375</v>
       </c>
       <c r="I20" s="10">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="J20" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K20" s="10"/>
       <c r="L20" s="10">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="M20" s="10">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="N20" s="10">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="O20" s="13">
-        <v>0.52631578947368418</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="P20" s="12">
-        <v>60.299570419397952</v>
-      </c>
-      <c r="Q20" s="1">
-        <v>2</v>
-      </c>
+        <v>60.192988668555238</v>
+      </c>
+      <c r="Q20" s="1"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E21" s="10">
-        <v>22475</v>
+        <v>40528</v>
       </c>
       <c r="F21" s="10">
-        <v>1059</v>
+        <v>1930</v>
       </c>
       <c r="G21" s="11">
-        <v>63.668555240793197</v>
+        <v>62.996891191709842</v>
       </c>
       <c r="H21" s="12">
-        <v>1.375</v>
+        <v>1.3068181818181819</v>
       </c>
       <c r="I21" s="10">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="J21" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K21" s="10"/>
       <c r="L21" s="10">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="M21" s="10">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="N21" s="10">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="O21" s="13">
-        <v>0.52083333333333337</v>
+        <v>0.53409090909090906</v>
       </c>
       <c r="P21" s="12">
-        <v>60.192988668555238</v>
-      </c>
-      <c r="Q21" s="1"/>
+        <v>60.120551106924154</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="E22" s="10">
-        <v>35239</v>
+        <v>29849</v>
       </c>
       <c r="F22" s="10">
-        <v>1637</v>
+        <v>1447</v>
       </c>
       <c r="G22" s="11">
-        <v>64.57971899816738</v>
+        <v>61.884588804422947</v>
       </c>
       <c r="H22" s="12">
-        <v>1.4605263157894737</v>
+        <v>1.078125</v>
       </c>
       <c r="I22" s="10">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="J22" s="10">
+        <v>4</v>
+      </c>
+      <c r="K22" s="10">
         <v>1</v>
       </c>
-      <c r="K22" s="10"/>
       <c r="L22" s="10">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="M22" s="10">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="N22" s="10">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O22" s="13">
-        <v>0.46052631578947367</v>
+        <v>0.515625</v>
       </c>
       <c r="P22" s="12">
-        <v>59.021592772401377</v>
+        <v>58.787962163096061</v>
       </c>
       <c r="Q22" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="E23" s="10">
-        <v>34459</v>
+        <v>25811</v>
       </c>
       <c r="F23" s="10">
-        <v>1687</v>
+        <v>1262</v>
       </c>
       <c r="G23" s="11">
-        <v>61.278601066982802</v>
+        <v>61.357369255150559</v>
       </c>
       <c r="H23" s="12">
-        <v>1.3552631578947369</v>
+        <v>1.1428571428571428</v>
       </c>
       <c r="I23" s="10">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="J23" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K23" s="10"/>
       <c r="L23" s="10">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="M23" s="10">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="N23" s="10">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="O23" s="13">
-        <v>0.47368421052631576</v>
+        <v>0.5</v>
       </c>
       <c r="P23" s="12">
-        <v>57.105547062677431</v>
+        <v>57.950158478605388</v>
       </c>
       <c r="Q23" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>41</v>
       </c>
       <c r="E24" s="10">
-        <v>34231</v>
+        <v>40283</v>
       </c>
       <c r="F24" s="10">
-        <v>1668</v>
+        <v>2019</v>
       </c>
       <c r="G24" s="11">
-        <v>61.56654676258993</v>
+        <v>59.855869242199105</v>
       </c>
       <c r="H24" s="12">
-        <v>1.131578947368421</v>
+        <v>1.3636363636363635</v>
       </c>
       <c r="I24" s="10">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="J24" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K24" s="10"/>
       <c r="L24" s="10">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="M24" s="10">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="N24" s="10">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="O24" s="13">
-        <v>0.43421052631578949</v>
+        <v>0.51136363636363635</v>
       </c>
       <c r="P24" s="12">
-        <v>56.122898523286636</v>
+        <v>57.240017560448464</v>
       </c>
       <c r="Q24" s="1">
         <v>4</v>
@@ -2098,48 +2062,50 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="E25" s="10">
-        <v>20215</v>
+        <v>39706</v>
       </c>
       <c r="F25" s="10">
-        <v>1016</v>
+        <v>1952</v>
       </c>
       <c r="G25" s="11">
-        <v>59.689960629921259</v>
+        <v>61.023565573770483</v>
       </c>
       <c r="H25" s="12">
-        <v>1.1818181818181819</v>
+        <v>1.1477272727272727</v>
       </c>
       <c r="I25" s="10">
-        <v>52</v>
-      </c>
-      <c r="J25" s="10"/>
+        <v>101</v>
+      </c>
+      <c r="J25" s="10">
+        <v>2</v>
+      </c>
       <c r="K25" s="10"/>
       <c r="L25" s="10">
         <v>114</v>
       </c>
       <c r="M25" s="10">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="N25" s="10">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="O25" s="13">
-        <v>0.45454545454545453</v>
+        <v>0.44318181818181818</v>
       </c>
       <c r="P25" s="12">
-        <v>55.419336077308515</v>
+        <v>56.011950447093881</v>
       </c>
       <c r="Q25" s="1"/>
     </row>
@@ -2157,40 +2123,42 @@
         <v>41</v>
       </c>
       <c r="E26" s="10">
-        <v>34282</v>
+        <v>39907</v>
       </c>
       <c r="F26" s="10">
-        <v>1660</v>
+        <v>1946</v>
       </c>
       <c r="G26" s="11">
-        <v>61.955421686746988</v>
+        <v>61.521582733812949</v>
       </c>
       <c r="H26" s="12">
-        <v>1.25</v>
+        <v>1.2727272727272727</v>
       </c>
       <c r="I26" s="10">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="J26" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K26" s="10"/>
       <c r="L26" s="10">
         <v>149</v>
       </c>
       <c r="M26" s="10">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="N26" s="10">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="O26" s="13">
-        <v>0.39473684210526316</v>
+        <v>0.39772727272727271</v>
       </c>
       <c r="P26" s="12">
-        <v>55.210900443880789</v>
-      </c>
-      <c r="Q26" s="1"/>
+        <v>54.99692609548724</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>4</v>
+      </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
@@ -2206,19 +2174,19 @@
         <v>41</v>
       </c>
       <c r="E27" s="10">
-        <v>30168</v>
+        <v>35794</v>
       </c>
       <c r="F27" s="10">
-        <v>1488</v>
+        <v>1774</v>
       </c>
       <c r="G27" s="11">
-        <v>60.822580645161288</v>
+        <v>60.531003382187151</v>
       </c>
       <c r="H27" s="12">
-        <v>1.1323529411764706</v>
+        <v>1.125</v>
       </c>
       <c r="I27" s="10">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J27" s="10">
         <v>2</v>
@@ -2228,19 +2196,19 @@
         <v>95</v>
       </c>
       <c r="M27" s="10">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="N27" s="10">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="O27" s="13">
-        <v>0.36764705882352944</v>
+        <v>0.41249999999999998</v>
       </c>
       <c r="P27" s="12">
-        <v>53.605218216318782</v>
+        <v>54.746702367531</v>
       </c>
       <c r="Q27" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -2257,149 +2225,151 @@
         <v>41</v>
       </c>
       <c r="E28" s="10">
-        <v>33174</v>
+        <v>38387</v>
       </c>
       <c r="F28" s="10">
-        <v>1673</v>
+        <v>1933</v>
       </c>
       <c r="G28" s="11">
-        <v>59.487148834429163</v>
+        <v>59.576306259699948</v>
       </c>
       <c r="H28" s="12">
-        <v>1</v>
+        <v>1.1136363636363635</v>
       </c>
       <c r="I28" s="10">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="J28" s="10">
         <v>3</v>
       </c>
       <c r="K28" s="10"/>
       <c r="L28" s="10">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="M28" s="10">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="N28" s="10">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="O28" s="13">
-        <v>0.30263157894736842</v>
+        <v>0.32954545454545453</v>
       </c>
       <c r="P28" s="12">
-        <v>50.719951552521465</v>
+        <v>51.589778018153595</v>
       </c>
       <c r="Q28" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B29" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="10">
+        <v>37186</v>
+      </c>
+      <c r="F29" s="10">
+        <v>1931</v>
+      </c>
+      <c r="G29" s="11">
+        <v>57.772138788192649</v>
+      </c>
+      <c r="H29" s="12">
+        <v>0.9642857142857143</v>
+      </c>
+      <c r="I29" s="10">
         <v>81</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" s="10">
-        <v>27526</v>
-      </c>
-      <c r="F29" s="10">
-        <v>1447</v>
-      </c>
-      <c r="G29" s="11">
-        <v>57.068417415342083</v>
-      </c>
-      <c r="H29" s="12">
-        <v>0.890625</v>
-      </c>
-      <c r="I29" s="10">
-        <v>57</v>
-      </c>
       <c r="J29" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="10"/>
       <c r="L29" s="10">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="M29" s="10">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="N29" s="10">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="O29" s="13">
-        <v>0.328125</v>
+        <v>0.32142857142857145</v>
       </c>
       <c r="P29" s="12">
-        <v>49.791642190739452</v>
+        <v>50.083354294591999</v>
       </c>
       <c r="Q29" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="E30" s="10">
-        <v>32137</v>
+        <v>27526</v>
       </c>
       <c r="F30" s="10">
-        <v>1734</v>
+        <v>1447</v>
       </c>
       <c r="G30" s="11">
-        <v>55.600346020761243</v>
+        <v>57.068417415342083</v>
       </c>
       <c r="H30" s="12">
-        <v>0.57894736842105265</v>
+        <v>0.890625</v>
       </c>
       <c r="I30" s="10">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="J30" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K30" s="10"/>
       <c r="L30" s="10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M30" s="10">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="N30" s="10">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O30" s="13">
-        <v>0.34210526315789475</v>
+        <v>0.328125</v>
       </c>
       <c r="P30" s="12">
-        <v>49.183400109269712</v>
-      </c>
-      <c r="Q30" s="1"/>
+        <v>49.791642190739452</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C31" s="10" t="s">
         <v>35</v>
@@ -2408,41 +2378,41 @@
         <v>20</v>
       </c>
       <c r="E31" s="10">
-        <v>31568</v>
+        <v>37110</v>
       </c>
       <c r="F31" s="10">
-        <v>1636</v>
+        <v>2050</v>
       </c>
       <c r="G31" s="11">
-        <v>57.88753056234718</v>
+        <v>54.307317073170729</v>
       </c>
       <c r="H31" s="12">
-        <v>0.94444444444444442</v>
+        <v>0.57954545454545459</v>
       </c>
       <c r="I31" s="10">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="J31" s="10">
         <v>2</v>
       </c>
       <c r="K31" s="10"/>
       <c r="L31" s="10">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="M31" s="10">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="N31" s="10">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="O31" s="13">
-        <v>0.27777777777777779</v>
+        <v>0.32954545454545453</v>
       </c>
       <c r="P31" s="12">
-        <v>48.854604726976362</v>
+        <v>47.901485587583139</v>
       </c>
       <c r="Q31" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -2459,16 +2429,16 @@
         <v>90</v>
       </c>
       <c r="E32" s="10">
-        <v>31776</v>
+        <v>36104</v>
       </c>
       <c r="F32" s="10">
-        <v>1716</v>
+        <v>2006</v>
       </c>
       <c r="G32" s="11">
-        <v>55.552447552447546</v>
+        <v>53.99401794616152</v>
       </c>
       <c r="H32" s="12">
-        <v>0.86842105263157898</v>
+        <v>0.75</v>
       </c>
       <c r="I32" s="10">
         <v>66</v>
@@ -2481,22 +2451,22 @@
         <v>80</v>
       </c>
       <c r="M32" s="10">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="N32" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O32" s="13">
-        <v>0.30263157894736842</v>
+        <v>0.27272727272727271</v>
       </c>
       <c r="P32" s="12">
-        <v>47.965660655134336</v>
+        <v>45.97763074413124</v>
       </c>
       <c r="Q32" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>99</v>
       </c>
@@ -2510,19 +2480,19 @@
         <v>41</v>
       </c>
       <c r="E33" s="10">
-        <v>15462</v>
+        <v>18825</v>
       </c>
       <c r="F33" s="10">
-        <v>933</v>
+        <v>1143</v>
       </c>
       <c r="G33" s="11">
-        <v>49.717041800643088</v>
+        <v>49.409448818897637</v>
       </c>
       <c r="H33" s="12">
-        <v>0.5</v>
+        <v>0.52173913043478259</v>
       </c>
       <c r="I33" s="10">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J33" s="10">
         <v>1</v>
@@ -2532,22 +2502,20 @@
         <v>60</v>
       </c>
       <c r="M33" s="10">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="N33" s="10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O33" s="13">
-        <v>0.21052631578947367</v>
+        <v>0.2391304347826087</v>
       </c>
       <c r="P33" s="12">
-        <v>41.117718734134371</v>
-      </c>
-      <c r="Q33" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+        <v>41.760527216706599</v>
+      </c>
+      <c r="Q33" s="1"/>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>93</v>
       </c>
@@ -2561,19 +2529,19 @@
         <v>41</v>
       </c>
       <c r="E34" s="10">
-        <v>32674</v>
+        <v>37507</v>
       </c>
       <c r="F34" s="10">
-        <v>1899</v>
+        <v>2191</v>
       </c>
       <c r="G34" s="11">
-        <v>51.617693522906791</v>
+        <v>51.356001825650395</v>
       </c>
       <c r="H34" s="12">
-        <v>0.93421052631578949</v>
+        <v>0.84090909090909094</v>
       </c>
       <c r="I34" s="10">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="J34" s="10"/>
       <c r="K34" s="10"/>
@@ -2581,22 +2549,22 @@
         <v>76</v>
       </c>
       <c r="M34" s="10">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="N34" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O34" s="13">
-        <v>0.14473684210526316</v>
+        <v>0.13636363636363635</v>
       </c>
       <c r="P34" s="12">
-        <v>40.474490729192645</v>
+        <v>40.040110368864362</v>
       </c>
       <c r="Q34" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>95</v>
       </c>
@@ -2643,7 +2611,7 @@
       </c>
       <c r="Q35" s="10"/>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>103</v>
       </c>
@@ -2690,7 +2658,7 @@
       </c>
       <c r="Q36" s="10"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>97</v>
       </c>
@@ -2704,19 +2672,19 @@
         <v>41</v>
       </c>
       <c r="E37" s="10">
-        <v>8576</v>
+        <v>14183</v>
       </c>
       <c r="F37" s="10">
-        <v>477</v>
+        <v>800</v>
       </c>
       <c r="G37" s="11">
-        <v>53.937106918238996</v>
+        <v>53.186250000000001</v>
       </c>
       <c r="H37" s="12">
-        <v>0.9</v>
+        <v>0.875</v>
       </c>
       <c r="I37" s="10">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
@@ -2724,20 +2692,20 @@
         <v>70</v>
       </c>
       <c r="M37" s="10">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="N37" s="10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O37" s="13">
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="P37" s="12">
-        <v>45.255974842767294</v>
+        <v>46.605374999999995</v>
       </c>
       <c r="Q37" s="10"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>105</v>
       </c>
@@ -2782,7 +2750,7 @@
       </c>
       <c r="Q38" s="10"/>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
         <v>108</v>
       </c>
@@ -2829,103 +2797,104 @@
       </c>
       <c r="Q39" s="10"/>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="E40" s="10">
-        <v>12910</v>
+        <v>11072</v>
       </c>
       <c r="F40" s="10">
-        <v>772</v>
+        <v>678</v>
       </c>
       <c r="G40" s="11">
-        <v>50.168393782383419</v>
+        <v>48.991150442477874</v>
       </c>
       <c r="H40" s="12">
-        <v>0.65625</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="I40" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
       <c r="L40" s="10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M40" s="10">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="N40" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O40" s="13">
-        <v>0.1875</v>
+        <v>0.20833333333333334</v>
       </c>
       <c r="P40" s="12">
-        <v>40.742875647668392</v>
-      </c>
-      <c r="Q40" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+        <v>40.543805309734509</v>
+      </c>
+      <c r="Q40" s="10"/>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="E41" s="10">
-        <v>11072</v>
+        <v>14212</v>
       </c>
       <c r="F41" s="10">
-        <v>678</v>
+        <v>862</v>
       </c>
       <c r="G41" s="11">
-        <v>48.991150442477874</v>
+        <v>49.461716937354993</v>
       </c>
       <c r="H41" s="12">
-        <v>0.91666666666666663</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="I41" s="10">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
       <c r="L41" s="10">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M41" s="10">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="N41" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O41" s="13">
-        <v>0.20833333333333334</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="P41" s="12">
-        <v>40.543805309734509</v>
-      </c>
-      <c r="Q41" s="10"/>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+        <v>39.623201856148491</v>
+      </c>
+      <c r="Q41" s="10">
+        <v>1</v>
+      </c>
+      <c r="U41" s="9"/>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>110</v>
       </c>
@@ -2939,13 +2908,13 @@
         <v>41</v>
       </c>
       <c r="E42" s="10">
-        <v>4661</v>
+        <v>4740</v>
       </c>
       <c r="F42" s="10">
         <v>294</v>
       </c>
       <c r="G42" s="11">
-        <v>47.561224489795919</v>
+        <v>48.367346938775512</v>
       </c>
       <c r="H42" s="12">
         <v>0.75</v>
@@ -2966,9 +2935,52 @@
         <v>0</v>
       </c>
       <c r="P42" s="12">
-        <v>33.292857142857144</v>
+        <v>33.857142857142854</v>
       </c>
       <c r="Q42" s="10"/>
+      <c r="U42" s="9"/>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U43" s="9"/>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U44" s="9"/>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U45" s="9"/>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U46" s="9"/>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U47" s="9"/>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U48" s="9"/>
+    </row>
+    <row r="50" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O50" s="9"/>
+    </row>
+    <row r="51" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O51" s="9"/>
+    </row>
+    <row r="52" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O52" s="9"/>
+    </row>
+    <row r="53" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O53" s="9"/>
+    </row>
+    <row r="54" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O54" s="9"/>
+    </row>
+    <row r="55" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O55" s="9"/>
+    </row>
+    <row r="56" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O56" s="9"/>
+    </row>
+    <row r="57" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O57" s="9"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A34">
